--- a/data-raw/data-tidy/public-site/nbs-RD-bulletin/02-xls/2023.xlsx
+++ b/data-raw/data-tidy/public-site/nbs-RD-bulletin/02-xls/2023.xlsx
@@ -1,159 +1,179 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\techme\data-raw\data-tidy\public-site\nbs-RD-bulletin\02-xls\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01163E84-555D-44C1-992C-88F9CAB29026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
-  <si>
-    <t xml:space="preserve">province</t>
-  </si>
-  <si>
-    <t xml:space="preserve">year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chn_block4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全国</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RD经费</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v4_ztr_jf_RD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">北京</t>
-  </si>
-  <si>
-    <t xml:space="preserve">天津</t>
-  </si>
-  <si>
-    <t xml:space="preserve">河北</t>
-  </si>
-  <si>
-    <t xml:space="preserve">山西</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内蒙古</t>
-  </si>
-  <si>
-    <t xml:space="preserve">辽宁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">吉林</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黑龙江</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上海</t>
-  </si>
-  <si>
-    <t xml:space="preserve">江苏</t>
-  </si>
-  <si>
-    <t xml:space="preserve">浙江</t>
-  </si>
-  <si>
-    <t xml:space="preserve">安徽</t>
-  </si>
-  <si>
-    <t xml:space="preserve">福建</t>
-  </si>
-  <si>
-    <t xml:space="preserve">江西</t>
-  </si>
-  <si>
-    <t xml:space="preserve">山东</t>
-  </si>
-  <si>
-    <t xml:space="preserve">河南</t>
-  </si>
-  <si>
-    <t xml:space="preserve">湖北</t>
-  </si>
-  <si>
-    <t xml:space="preserve">湖南</t>
-  </si>
-  <si>
-    <t xml:space="preserve">广东</t>
-  </si>
-  <si>
-    <t xml:space="preserve">广西</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海南</t>
-  </si>
-  <si>
-    <t xml:space="preserve">重庆</t>
-  </si>
-  <si>
-    <t xml:space="preserve">四川</t>
-  </si>
-  <si>
-    <t xml:space="preserve">贵州</t>
-  </si>
-  <si>
-    <t xml:space="preserve">云南</t>
-  </si>
-  <si>
-    <t xml:space="preserve">西藏</t>
-  </si>
-  <si>
-    <t xml:space="preserve">陕西</t>
-  </si>
-  <si>
-    <t xml:space="preserve">甘肃</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青海</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宁夏</t>
-  </si>
-  <si>
-    <t xml:space="preserve">新疆</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RD强度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v4_ztr_qd_RD</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="45">
+  <si>
+    <t>province</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>chn_block4</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>units</t>
+  </si>
+  <si>
+    <t>variables</t>
+  </si>
+  <si>
+    <t>全国</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>RD经费</t>
+  </si>
+  <si>
+    <t>v4_ztr_jf_RD</t>
+  </si>
+  <si>
+    <t>北京</t>
+  </si>
+  <si>
+    <t>天津</t>
+  </si>
+  <si>
+    <t>河北</t>
+  </si>
+  <si>
+    <t>山西</t>
+  </si>
+  <si>
+    <t>内蒙古</t>
+  </si>
+  <si>
+    <t>辽宁</t>
+  </si>
+  <si>
+    <t>吉林</t>
+  </si>
+  <si>
+    <t>黑龙江</t>
+  </si>
+  <si>
+    <t>上海</t>
+  </si>
+  <si>
+    <t>江苏</t>
+  </si>
+  <si>
+    <t>浙江</t>
+  </si>
+  <si>
+    <t>安徽</t>
+  </si>
+  <si>
+    <t>福建</t>
+  </si>
+  <si>
+    <t>江西</t>
+  </si>
+  <si>
+    <t>山东</t>
+  </si>
+  <si>
+    <t>河南</t>
+  </si>
+  <si>
+    <t>湖北</t>
+  </si>
+  <si>
+    <t>湖南</t>
+  </si>
+  <si>
+    <t>广东</t>
+  </si>
+  <si>
+    <t>广西</t>
+  </si>
+  <si>
+    <t>海南</t>
+  </si>
+  <si>
+    <t>重庆</t>
+  </si>
+  <si>
+    <t>四川</t>
+  </si>
+  <si>
+    <t>贵州</t>
+  </si>
+  <si>
+    <t>云南</t>
+  </si>
+  <si>
+    <t>西藏</t>
+  </si>
+  <si>
+    <t>陕西</t>
+  </si>
+  <si>
+    <t>甘肃</t>
+  </si>
+  <si>
+    <t>青海</t>
+  </si>
+  <si>
+    <t>宁夏</t>
+  </si>
+  <si>
+    <t>新疆</t>
+  </si>
+  <si>
+    <t>RD强度</t>
+  </si>
+  <si>
+    <t>v4_ztr_qd_RD</t>
+  </si>
+  <si>
+    <t>亿元</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -181,9 +201,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -465,11 +494,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F65"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,7 +518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -499,15 +528,17 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>33357.1</v>
       </c>
-      <c r="E2"/>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
       <c r="F2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -517,15 +548,17 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>2947.1</v>
       </c>
-      <c r="E3"/>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -535,15 +568,17 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="n">
-        <v>599.2</v>
-      </c>
-      <c r="E4"/>
+      <c r="D4">
+        <v>599.20000000000005</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -553,15 +588,17 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>912.1</v>
       </c>
-      <c r="E5"/>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -571,15 +608,17 @@
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>298.2</v>
       </c>
-      <c r="E6"/>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
       <c r="F6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -589,15 +628,17 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>228.1</v>
       </c>
-      <c r="E7"/>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -607,15 +648,17 @@
       <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>676.4</v>
       </c>
-      <c r="E8"/>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
       <c r="F8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -625,15 +668,17 @@
       <c r="C9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>210.2</v>
       </c>
-      <c r="E9"/>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
       <c r="F9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -643,15 +688,17 @@
       <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>229.3</v>
       </c>
-      <c r="E10"/>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
       <c r="F10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -661,15 +708,17 @@
       <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>2049.6</v>
       </c>
-      <c r="E11"/>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
       <c r="F11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -679,15 +728,17 @@
       <c r="C12" t="s">
         <v>8</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>4212.3</v>
       </c>
-      <c r="E12"/>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
       <c r="F12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -697,15 +748,17 @@
       <c r="C13" t="s">
         <v>8</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>2640.2</v>
       </c>
-      <c r="E13"/>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
       <c r="F13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -715,15 +768,17 @@
       <c r="C14" t="s">
         <v>8</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>1264.7</v>
       </c>
-      <c r="E14"/>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
       <c r="F14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -733,15 +788,17 @@
       <c r="C15" t="s">
         <v>8</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>1171.7</v>
       </c>
-      <c r="E15"/>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
       <c r="F15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -751,15 +808,17 @@
       <c r="C16" t="s">
         <v>8</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>604.1</v>
       </c>
-      <c r="E16"/>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
       <c r="F16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -769,15 +828,17 @@
       <c r="C17" t="s">
         <v>8</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>2386</v>
       </c>
-      <c r="E17"/>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -787,15 +848,17 @@
       <c r="C18" t="s">
         <v>8</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>1211.7</v>
       </c>
-      <c r="E18"/>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
       <c r="F18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -805,15 +868,17 @@
       <c r="C19" t="s">
         <v>8</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>1408.2</v>
       </c>
-      <c r="E19"/>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
       <c r="F19" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -823,15 +888,17 @@
       <c r="C20" t="s">
         <v>8</v>
       </c>
-      <c r="D20" t="n">
-        <v>1283.9</v>
-      </c>
-      <c r="E20"/>
+      <c r="D20">
+        <v>1283.9000000000001</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
       <c r="F20" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -841,15 +908,17 @@
       <c r="C21" t="s">
         <v>8</v>
       </c>
-      <c r="D21" t="n">
-        <v>4802.6</v>
-      </c>
-      <c r="E21"/>
+      <c r="D21">
+        <v>4802.6000000000004</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -859,15 +928,17 @@
       <c r="C22" t="s">
         <v>8</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>228.1</v>
       </c>
-      <c r="E22"/>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
       <c r="F22" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -877,15 +948,17 @@
       <c r="C23" t="s">
         <v>8</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>89.8</v>
       </c>
-      <c r="E23"/>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
       <c r="F23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -895,15 +968,17 @@
       <c r="C24" t="s">
         <v>8</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>746.7</v>
       </c>
-      <c r="E24"/>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
       <c r="F24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -913,15 +988,17 @@
       <c r="C25" t="s">
         <v>8</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>1357.8</v>
       </c>
-      <c r="E25"/>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
       <c r="F25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -931,15 +1008,17 @@
       <c r="C26" t="s">
         <v>8</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>211.4</v>
       </c>
-      <c r="E26"/>
+      <c r="E26" t="s">
+        <v>43</v>
+      </c>
       <c r="F26" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -949,15 +1028,17 @@
       <c r="C27" t="s">
         <v>8</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>346.7</v>
       </c>
-      <c r="E27"/>
+      <c r="E27" t="s">
+        <v>43</v>
+      </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -967,15 +1048,17 @@
       <c r="C28" t="s">
         <v>8</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>7.2</v>
       </c>
-      <c r="E28"/>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
       <c r="F28" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -985,15 +1068,17 @@
       <c r="C29" t="s">
         <v>8</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>846</v>
       </c>
-      <c r="E29"/>
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
       <c r="F29" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1003,15 +1088,17 @@
       <c r="C30" t="s">
         <v>8</v>
       </c>
-      <c r="D30" t="n">
-        <v>156.2</v>
-      </c>
-      <c r="E30"/>
+      <c r="D30">
+        <v>156.19999999999999</v>
+      </c>
+      <c r="E30" t="s">
+        <v>43</v>
+      </c>
       <c r="F30" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -1021,15 +1108,17 @@
       <c r="C31" t="s">
         <v>8</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>30.3</v>
       </c>
-      <c r="E31"/>
+      <c r="E31" t="s">
+        <v>43</v>
+      </c>
       <c r="F31" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -1039,15 +1128,17 @@
       <c r="C32" t="s">
         <v>8</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>85.5</v>
       </c>
-      <c r="E32"/>
+      <c r="E32" t="s">
+        <v>43</v>
+      </c>
       <c r="F32" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -1057,15 +1148,17 @@
       <c r="C33" t="s">
         <v>8</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>115.5</v>
       </c>
-      <c r="E33"/>
+      <c r="E33" t="s">
+        <v>43</v>
+      </c>
       <c r="F33" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1075,15 +1168,17 @@
       <c r="C34" t="s">
         <v>41</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>2.65</v>
       </c>
-      <c r="E34"/>
+      <c r="E34" t="s">
+        <v>44</v>
+      </c>
       <c r="F34" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -1093,15 +1188,17 @@
       <c r="C35" t="s">
         <v>41</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>6.73</v>
       </c>
-      <c r="E35"/>
+      <c r="E35" t="s">
+        <v>44</v>
+      </c>
       <c r="F35" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -1111,15 +1208,17 @@
       <c r="C36" t="s">
         <v>41</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>3.58</v>
       </c>
-      <c r="E36"/>
+      <c r="E36" t="s">
+        <v>44</v>
+      </c>
       <c r="F36" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -1129,15 +1228,17 @@
       <c r="C37" t="s">
         <v>41</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>2.08</v>
       </c>
-      <c r="E37"/>
+      <c r="E37" t="s">
+        <v>44</v>
+      </c>
       <c r="F37" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -1147,15 +1248,17 @@
       <c r="C38" t="s">
         <v>41</v>
       </c>
-      <c r="D38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E38"/>
+      <c r="D38">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E38" t="s">
+        <v>44</v>
+      </c>
       <c r="F38" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -1165,15 +1268,17 @@
       <c r="C39" t="s">
         <v>41</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>0.93</v>
       </c>
-      <c r="E39"/>
+      <c r="E39" t="s">
+        <v>44</v>
+      </c>
       <c r="F39" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -1183,15 +1288,17 @@
       <c r="C40" t="s">
         <v>41</v>
       </c>
-      <c r="D40" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="E40"/>
+      <c r="D40">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="E40" t="s">
+        <v>44</v>
+      </c>
       <c r="F40" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>16</v>
       </c>
@@ -1201,15 +1308,17 @@
       <c r="C41" t="s">
         <v>41</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>1.55</v>
       </c>
-      <c r="E41"/>
+      <c r="E41" t="s">
+        <v>44</v>
+      </c>
       <c r="F41" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -1219,15 +1328,17 @@
       <c r="C42" t="s">
         <v>41</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>1.44</v>
       </c>
-      <c r="E42"/>
+      <c r="E42" t="s">
+        <v>44</v>
+      </c>
       <c r="F42" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -1237,15 +1348,17 @@
       <c r="C43" t="s">
         <v>41</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>4.34</v>
       </c>
-      <c r="E43"/>
+      <c r="E43" t="s">
+        <v>44</v>
+      </c>
       <c r="F43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -1255,15 +1368,17 @@
       <c r="C44" t="s">
         <v>41</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>3.29</v>
       </c>
-      <c r="E44"/>
+      <c r="E44" t="s">
+        <v>44</v>
+      </c>
       <c r="F44" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -1273,15 +1388,17 @@
       <c r="C45" t="s">
         <v>41</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>3.2</v>
       </c>
-      <c r="E45"/>
+      <c r="E45" t="s">
+        <v>44</v>
+      </c>
       <c r="F45" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -1291,15 +1408,17 @@
       <c r="C46" t="s">
         <v>41</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>2.69</v>
       </c>
-      <c r="E46"/>
+      <c r="E46" t="s">
+        <v>44</v>
+      </c>
       <c r="F46" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -1309,15 +1428,17 @@
       <c r="C47" t="s">
         <v>41</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>2.16</v>
       </c>
-      <c r="E47"/>
+      <c r="E47" t="s">
+        <v>44</v>
+      </c>
       <c r="F47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -1327,15 +1448,17 @@
       <c r="C48" t="s">
         <v>41</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>1.88</v>
       </c>
-      <c r="E48"/>
+      <c r="E48" t="s">
+        <v>44</v>
+      </c>
       <c r="F48" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -1345,15 +1468,17 @@
       <c r="C49" t="s">
         <v>41</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>2.59</v>
       </c>
-      <c r="E49"/>
+      <c r="E49" t="s">
+        <v>44</v>
+      </c>
       <c r="F49" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -1363,15 +1488,17 @@
       <c r="C50" t="s">
         <v>41</v>
       </c>
-      <c r="D50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E50"/>
+      <c r="D50">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="E50" t="s">
+        <v>44</v>
+      </c>
       <c r="F50" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>26</v>
       </c>
@@ -1381,15 +1508,17 @@
       <c r="C51" t="s">
         <v>41</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>2.52</v>
       </c>
-      <c r="E51"/>
+      <c r="E51" t="s">
+        <v>44</v>
+      </c>
       <c r="F51" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>27</v>
       </c>
@@ -1399,15 +1528,17 @@
       <c r="C52" t="s">
         <v>41</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>2.57</v>
       </c>
-      <c r="E52"/>
+      <c r="E52" t="s">
+        <v>44</v>
+      </c>
       <c r="F52" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>28</v>
       </c>
@@ -1417,15 +1548,17 @@
       <c r="C53" t="s">
         <v>41</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>3.54</v>
       </c>
-      <c r="E53"/>
+      <c r="E53" t="s">
+        <v>44</v>
+      </c>
       <c r="F53" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -1435,15 +1568,17 @@
       <c r="C54" t="s">
         <v>41</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>0.84</v>
       </c>
-      <c r="E54"/>
+      <c r="E54" t="s">
+        <v>44</v>
+      </c>
       <c r="F54" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>30</v>
       </c>
@@ -1453,15 +1588,17 @@
       <c r="C55" t="s">
         <v>41</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>1.19</v>
       </c>
-      <c r="E55"/>
+      <c r="E55" t="s">
+        <v>44</v>
+      </c>
       <c r="F55" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -1471,15 +1608,17 @@
       <c r="C56" t="s">
         <v>41</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>2.48</v>
       </c>
-      <c r="E56"/>
+      <c r="E56" t="s">
+        <v>44</v>
+      </c>
       <c r="F56" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>32</v>
       </c>
@@ -1489,15 +1628,17 @@
       <c r="C57" t="s">
         <v>41</v>
       </c>
-      <c r="D57" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="E57"/>
+      <c r="D57">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="E57" t="s">
+        <v>44</v>
+      </c>
       <c r="F57" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>33</v>
       </c>
@@ -1507,15 +1648,17 @@
       <c r="C58" t="s">
         <v>41</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>1.01</v>
       </c>
-      <c r="E58"/>
+      <c r="E58" t="s">
+        <v>44</v>
+      </c>
       <c r="F58" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>34</v>
       </c>
@@ -1525,15 +1668,17 @@
       <c r="C59" t="s">
         <v>41</v>
       </c>
-      <c r="D59" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E59"/>
+      <c r="D59">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="E59" t="s">
+        <v>44</v>
+      </c>
       <c r="F59" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>35</v>
       </c>
@@ -1543,15 +1688,17 @@
       <c r="C60" t="s">
         <v>41</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>0.3</v>
       </c>
-      <c r="E60"/>
+      <c r="E60" t="s">
+        <v>44</v>
+      </c>
       <c r="F60" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>36</v>
       </c>
@@ -1561,15 +1708,17 @@
       <c r="C61" t="s">
         <v>41</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>2.5</v>
       </c>
-      <c r="E61"/>
+      <c r="E61" t="s">
+        <v>44</v>
+      </c>
       <c r="F61" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>37</v>
       </c>
@@ -1579,15 +1728,17 @@
       <c r="C62" t="s">
         <v>41</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>1.32</v>
       </c>
-      <c r="E62"/>
+      <c r="E62" t="s">
+        <v>44</v>
+      </c>
       <c r="F62" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>38</v>
       </c>
@@ -1597,15 +1748,17 @@
       <c r="C63" t="s">
         <v>41</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>0.8</v>
       </c>
-      <c r="E63"/>
+      <c r="E63" t="s">
+        <v>44</v>
+      </c>
       <c r="F63" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -1615,15 +1768,17 @@
       <c r="C64" t="s">
         <v>41</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>1.61</v>
       </c>
-      <c r="E64"/>
+      <c r="E64" t="s">
+        <v>44</v>
+      </c>
       <c r="F64" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>40</v>
       </c>
@@ -1633,16 +1788,19 @@
       <c r="C65" t="s">
         <v>41</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>0.6</v>
       </c>
-      <c r="E65"/>
+      <c r="E65" t="s">
+        <v>44</v>
+      </c>
       <c r="F65" t="s">
         <v>42</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>